--- a/tests/workbooktests/workbooks/test_date.xlsx
+++ b/tests/workbooktests/workbooks/test_date.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F935F4B1-8483-4C42-BCBF-7AF6C16EC6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B780ED8-F589-4B79-BCDB-902C58D25759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="qlPeriod" sheetId="1" r:id="rId1"/>
     <sheet name="qlDate" sheetId="2" r:id="rId2"/>
     <sheet name="qlDateParser" sheetId="3" r:id="rId3"/>
     <sheet name="qlPeriodParser" sheetId="4" r:id="rId4"/>
+    <sheet name="ECBDate" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>37d</t>
   </si>
@@ -169,6 +170,45 @@
   </si>
   <si>
     <t>1y3M</t>
+  </si>
+  <si>
+    <t>qlECBDate</t>
+  </si>
+  <si>
+    <t>qlECBCode</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>qlECBIsDate</t>
+  </si>
+  <si>
+    <t>qlECBIsCode</t>
+  </si>
+  <si>
+    <t>qlECBDateFromCode</t>
+  </si>
+  <si>
+    <t>qlECBNextDate</t>
+  </si>
+  <si>
+    <t>qlECBNextCode</t>
+  </si>
+  <si>
+    <t>qlECBNextDateFromCode</t>
+  </si>
+  <si>
+    <t>qlECBNextDates</t>
+  </si>
+  <si>
+    <t>qlECBNextDatesFromCode</t>
+  </si>
+  <si>
+    <t>qlECBNextCodeFromCode</t>
   </si>
 </sst>
 </file>
@@ -207,14 +247,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -493,61 +539,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="e" cm="1">
-        <f t="array" aca="1" ref="A3" ca="1">_xll.qlPeriodLength(A1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="e" cm="1">
-        <f t="array" aca="1" ref="A4" ca="1">_xll.qlPeriodFrequency(A1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="e" cm="1">
-        <f t="array" aca="1" ref="A5" ca="1">_xll.qlPeriodFrequency(A2)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="e" cm="1">
-        <f t="array" aca="1" ref="A6" ca="1">_xll.qlPeriodNormalized(A1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="e" cm="1">
-        <f t="array" aca="1" ref="A7" ca="1">_xll.qlPeriodNormalized(A2)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="e" cm="1">
-        <f t="array" aca="1" ref="A8" ca="1">_xll.qlPeriodUnits(A1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="e" cm="1">
-        <f t="array" aca="1" ref="A9" ca="1">_xll.qlPeriodUnits(A2)</f>
-        <v>#VALUE!</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" cm="1">
+        <f t="array" ref="A3">_xll.qlPeriodLength(A1)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="str" cm="1">
+        <f t="array" ref="A4">_xll.qlPeriodFrequency(A1)</f>
+        <v>ANNUAL</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="str" cm="1">
+        <f t="array" ref="A5">_xll.qlPeriodFrequency(A2)</f>
+        <v>OTHERFREQUENCY</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="str" cm="1">
+        <f t="array" ref="A6">_xll.qlPeriodNormalized(A1)</f>
+        <v>1Y</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="str" cm="1">
+        <f t="array" ref="A7">_xll.qlPeriodNormalized(A2)</f>
+        <v>37D</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="str" cm="1">
+        <f t="array" ref="A8">_xll.qlPeriodUnits(A1)</f>
+        <v>MONTHS</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="str" cm="1">
+        <f t="array" ref="A9">_xll.qlPeriodUnits(A2)</f>
+        <v>DAYS</v>
       </c>
     </row>
   </sheetData>
@@ -558,13 +604,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46906BE3-F11A-458F-9DD4-FCBD355E6523}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -572,7 +618,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -580,7 +626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -588,70 +634,70 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_xll.qlDate(B1,B2,B3)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" cm="1">
+        <f t="array" ref="B4">_xll.qlDate(B1,B2,B3)</f>
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="e" cm="1">
-        <f t="array" aca="1" ref="B5" ca="1">_xll.qlDateWeekday(B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="str" cm="1">
+        <f t="array" ref="B5">_xll.qlDateWeekday(B4)</f>
+        <v>SUNDAY</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="e" cm="1">
-        <f t="array" aca="1" ref="B6" ca="1">_xll.qlDateDayOfMonth(B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" cm="1">
+        <f t="array" ref="B6">_xll.qlDateDayOfMonth(B4)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">_xll.qlDateDayOfYear(B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" cm="1">
+        <f t="array" ref="B7">_xll.qlDateDayOfYear(B4)</f>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlDateMonth(B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" cm="1">
+        <f t="array" ref="B8">_xll.qlDateMonth(B4)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="e" cm="1">
-        <f t="array" aca="1" ref="B9" ca="1">_xll.qlDateYear(B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" cm="1">
+        <f t="array" ref="B9">_xll.qlDateYear(B4)</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="e" cm="1">
-        <f t="array" aca="1" ref="B10" ca="1">_xll.qlDateIsLeap(B9-2)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" t="b" cm="1">
+        <f t="array" ref="B10">_xll.qlDateIsLeap(B9-2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -659,7 +705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -667,7 +713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -675,43 +721,43 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B14" ca="1">_xll.qlDateStartOfMonth(B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" cm="1">
+        <f t="array" ref="B14">_xll.qlDateStartOfMonth(B4)</f>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlDateEndOfMonth(B4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" cm="1">
+        <f t="array" ref="B15">_xll.qlDateEndOfMonth(B4)</f>
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlDateIsStartOfMonth(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" t="b" cm="1">
+        <f t="array" ref="B16">_xll.qlDateIsStartOfMonth(B14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlDateIsEndOfMonth(B15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="b" cm="1">
+        <f t="array" ref="B17">_xll.qlDateIsEndOfMonth(B15)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -719,16 +765,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B19" ca="1">_xll.qlDateNextWeekday(B4,B18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" cm="1">
+        <f t="array" ref="B19">_xll.qlDateNextWeekday(B4,B18)</f>
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -736,13 +782,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">_xll.qlDateNthWeekday(B20,B18,B8,B9)</f>
-        <v>#VALUE!</v>
+      <c r="B21" s="1" cm="1">
+        <f t="array" ref="B21">_xll.qlDateNthWeekday(B20,B18,B8,B9)</f>
+        <v>46161</v>
       </c>
     </row>
   </sheetData>
@@ -753,13 +799,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10FA8D3-46AE-49A1-A85A-03A63DBCD87C}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -767,7 +813,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -775,7 +821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -783,22 +829,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_xll.qlDateParserParseFormatted(B1,B2)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" cm="1">
+        <f t="array" ref="B4">_xll.qlDateParserParseFormatted(B1,B2)</f>
+        <v>45394</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B5" ca="1">_xll.qlDateParserParseISO(B3)</f>
-        <v>#VALUE!</v>
+      <c r="B5" s="3" cm="1">
+        <f t="array" ref="B5">_xll.qlDateParserParseISO(B3)</f>
+        <v>45394</v>
       </c>
     </row>
   </sheetData>
@@ -809,12 +855,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD34B23F-20C4-4C32-94BC-89E68DE44435}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -822,16 +868,226 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlPeriodParserParse(B1)</f>
-        <v>#VALUE!</v>
+      <c r="B2" t="str" cm="1">
+        <f t="array" ref="B2">_xll.qlPeriodParserParse(B1)</f>
+        <v>15M</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EF73768-F0CE-4AE4-B3CB-3E1B89CB74FC}">
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="5" cm="1">
+        <f t="array" ref="B3">_xll.qlECBDate(B1,B2)</f>
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="5" t="str" cm="1">
+        <f t="array" ref="B4">_xll.qlECBCode(B3,B3)</f>
+        <v>NOV23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4" t="b" cm="1">
+        <f t="array" ref="B5">_xll.qlECBIsDate(B3,B3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="b" cm="1">
+        <f t="array" ref="B6">_xll.qlECBIsCode(B4,B4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="5" cm="1">
+        <f t="array" ref="B7">_xll.qlECBDateFromCode(B4,B4)</f>
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="5" cm="1">
+        <f t="array" ref="B8">_xll.qlECBNextDate(B3)</f>
+        <v>45280</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="4" t="str" cm="1">
+        <f t="array" ref="B9">_xll.qlECBNextCode(B3)</f>
+        <v>DEC23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="5" cm="1">
+        <f t="array" ref="B10">_xll.qlECBNextDateFromCode(B4)</f>
+        <v>45280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="5" cm="1">
+        <f t="array" ref="B11:B19">_xll.qlECBNextDates(B3)</f>
+        <v>45280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
+        <v>45364</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>45399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
+        <v>45455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>45497</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
+        <v>45553</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
+        <v>45588</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
+        <v>45644</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="5" cm="1">
+        <f t="array" ref="B20:B28">_xll.qlECBNextDatesFromCode(B4)</f>
+        <v>45280</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
+        <v>45364</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
+        <v>45399</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
+        <v>45455</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
+        <v>45497</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
+        <v>45553</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="5">
+        <v>45588</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="5">
+        <v>45644</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="4" t="str" cm="1">
+        <f t="array" ref="B29">_xll.qlECBNextCodeFromCode(B4)</f>
+        <v>DEC23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>